--- a/docs/gift-finder-tags.xlsx
+++ b/docs/gift-finder-tags.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1576,6 +1576,48 @@
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>가격리스트(xlsx)에 없는 항목 — script-guide.md 3-8 기준으로 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>blackwhite-rose-moodlamp</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>블랙앤화이트 장미 무드등</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>무드등</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>연인, 배우자, 친구</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>기념일, 생일, 프러포즈, 집들이·개업</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>인테리어형</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>받는 분의 방 색이나 취향을 몰라 어떤 색 꽃을 골라야 할지 망설여질 때</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>흰 장미와 검은 장미를 투명 케이스에 담아 어느 공간에나 어울리고, LED를 켜면 은은한 무드등이 돼요. 리본까지 묶어 보내 드려서 포장을 뜯지 않고 그대로 두시면 돼요.</t>
         </is>
       </c>
     </row>
